--- a/src/stp/database/2026-mens-world-cup.xlsx
+++ b/src/stp/database/2026-mens-world-cup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bruceoberg/code/soccer-tourney-poster/src/stp/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768EEF1E-CA39-9B41-9DF5-A37E58750E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B2A9B9-35A4-7843-97D3-A9BC7AD54869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="34200" windowHeight="19280" xr2:uid="{51C3DE88-701F-4CAC-8963-452186F7FFBA}"/>
+    <workbookView xWindow="17120" yWindow="680" windowWidth="17080" windowHeight="19760" activeTab="1" xr2:uid="{51C3DE88-701F-4CAC-8963-452186F7FFBA}"/>
   </bookViews>
   <sheets>
     <sheet name="Properties" sheetId="13" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="253">
   <si>
     <t>A1</t>
   </si>
@@ -868,31 +868,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="11">
     <dxf>
-      <numFmt numFmtId="164" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -937,25 +944,32 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D36B1D81-AA68-4E33-AA36-B206B4FF7406}" name="matches" displayName="matches" ref="A1:N105" totalsRowShown="0">
   <autoFilter ref="A1:N105" xr:uid="{D36B1D81-AA68-4E33-AA36-B206B4FF7406}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N105">
+    <sortCondition ref="D1:D105"/>
+  </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{35D3E9F5-BB3B-4940-9EB6-C927FD84875C}" name="match"/>
     <tableColumn id="2" xr3:uid="{97337EE3-AAC3-4452-8381-1A56C6B35138}" name="home-seed"/>
     <tableColumn id="3" xr3:uid="{AEDB8750-5B25-4357-9054-E49FECC94717}" name="away-seed"/>
-    <tableColumn id="4" xr3:uid="{B178F43D-E631-4314-9E59-2CDA6EDA94F1}" name="time" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{A42548B2-C8DF-4D47-B798-8E23FCB67696}" name="venue" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{FC876643-4BF9-4FDA-A0ED-DF50FF384B1F}" name="home-known" dataDxfId="6">
+    <tableColumn id="4" xr3:uid="{B178F43D-E631-4314-9E59-2CDA6EDA94F1}" name="time" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{A42548B2-C8DF-4D47-B798-8E23FCB67696}" name="venue" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{FC876643-4BF9-4FDA-A0ED-DF50FF384B1F}" name="home-known" dataDxfId="8">
       <calculatedColumnFormula>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{E5D59926-7D0A-4689-A049-F55DB0E286E9}" name="away-known" dataDxfId="5">
+    <tableColumn id="10" xr3:uid="{E5D59926-7D0A-4689-A049-F55DB0E286E9}" name="away-known" dataDxfId="7">
       <calculatedColumnFormula>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{1D7BA3FB-80F3-DD4D-AB1A-901F7CE41FBA}" name="home-team"/>
-    <tableColumn id="12" xr3:uid="{AC0139B3-7839-F243-81F2-C8F8601CBDE1}" name="away-team"/>
+    <tableColumn id="13" xr3:uid="{1D7BA3FB-80F3-DD4D-AB1A-901F7CE41FBA}" name="home-team" dataDxfId="6">
+      <calculatedColumnFormula>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{AC0139B3-7839-F243-81F2-C8F8601CBDE1}" name="away-team" dataDxfId="5">
+      <calculatedColumnFormula>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="6" xr3:uid="{A0CDBBB6-1128-45BC-8300-89FE399860C1}" name="home-score" dataDxfId="4"/>
     <tableColumn id="9" xr3:uid="{95DA1082-F87D-4A64-B45A-77AEEA888386}" name="away-score" dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{AF9504D2-0653-5049-AD21-E4B2A9F7499E}" name="after-extra-time" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{5865175D-2339-4B50-A707-595597D0BEF5}" name="home-tiebreaker" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{967E27DF-151D-40C4-9623-59691A5D7311}" name="away-tiebreaker" dataDxfId="0"/>
+    <tableColumn id="14" xr3:uid="{AF9504D2-0653-5049-AD21-E4B2A9F7499E}" name="after-extra-time" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{5865175D-2339-4B50-A707-595597D0BEF5}" name="home-tiebreaker" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{967E27DF-151D-40C4-9623-59691A5D7311}" name="away-tiebreaker" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1590,8 +1604,7 @@
   <cols>
     <col min="4" max="4" width="16.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.83203125" style="1"/>
-    <col min="10" max="10" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.1640625" style="1" customWidth="1"/>
     <col min="13" max="13" width="16.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -1665,6 +1678,23 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>RSA</v>
       </c>
+      <c r="H2" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>MEX</v>
+      </c>
+      <c r="I2" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>RSA</v>
+      </c>
+      <c r="J2" s="5">
+        <v>2</v>
+      </c>
+      <c r="K2" s="5">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3">
@@ -1690,6 +1720,23 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>CZE</v>
       </c>
+      <c r="H3" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>KOR</v>
+      </c>
+      <c r="I3" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>CZE</v>
+      </c>
+      <c r="J3" s="5">
+        <v>2</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4">
@@ -1715,6 +1762,23 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>BIH</v>
       </c>
+      <c r="H4" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>CAN</v>
+      </c>
+      <c r="I4" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>BIH</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5">
@@ -1740,181 +1804,317 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>PAR</v>
       </c>
+      <c r="H5" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>USA</v>
+      </c>
+      <c r="I5" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>PAR</v>
+      </c>
+      <c r="J5" s="5">
+        <v>4</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D6" s="4">
-        <v>46187.041666666664</v>
+        <v>46186.791666666664</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>HAI</v>
+        <v>QAT</v>
       </c>
       <c r="G6" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>SCO</v>
-      </c>
+        <v>SUI</v>
+      </c>
+      <c r="H6" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>QAT</v>
+      </c>
+      <c r="I6" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>SUI</v>
+      </c>
+      <c r="J6" s="5">
+        <v>1</v>
+      </c>
+      <c r="K6" s="5">
+        <v>1</v>
+      </c>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D7" s="4">
-        <v>46187.166666666664</v>
+        <v>46186.916666666664</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>AUS</v>
+        <v>BRA</v>
       </c>
       <c r="G7" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>TUR</v>
-      </c>
+        <v>MAR</v>
+      </c>
+      <c r="H7" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>BRA</v>
+      </c>
+      <c r="I7" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="J7" s="5">
+        <v>1</v>
+      </c>
+      <c r="K7" s="5">
+        <v>1</v>
+      </c>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D8" s="4">
-        <v>46186.916666666664</v>
+        <v>46187.041666666664</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F8" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>BRA</v>
+        <v>HAI</v>
       </c>
       <c r="G8" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>MAR</v>
-      </c>
+        <v>SCO</v>
+      </c>
+      <c r="H8" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>HAI</v>
+      </c>
+      <c r="I8" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>SCO</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>1</v>
+      </c>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D9" s="4">
-        <v>46186.791666666664</v>
+        <v>46187.166666666664</v>
       </c>
       <c r="E9">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F9" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>QAT</v>
+        <v>AUS</v>
       </c>
       <c r="G9" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>SUI</v>
-      </c>
+        <v>TUR</v>
+      </c>
+      <c r="H9" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>AUS</v>
+      </c>
+      <c r="I9" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>TUR</v>
+      </c>
+      <c r="J9" s="5">
+        <v>2</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4">
-        <v>46187.958333333328</v>
+        <v>46187.708333333328</v>
       </c>
       <c r="E10">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>CIV</v>
+        <v>GER</v>
       </c>
       <c r="G10" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>ECU</v>
-      </c>
+        <v>CUW</v>
+      </c>
+      <c r="H10" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>GER</v>
+      </c>
+      <c r="I10" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>CUW</v>
+      </c>
+      <c r="J10" s="5">
+        <v>7</v>
+      </c>
+      <c r="K10" s="5">
+        <v>1</v>
+      </c>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D11" s="4">
-        <v>46187.708333333328</v>
+        <v>46187.833333333328</v>
       </c>
       <c r="E11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>GER</v>
+        <v>NED</v>
       </c>
       <c r="G11" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>CUW</v>
-      </c>
+        <v>JPN</v>
+      </c>
+      <c r="H11" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>NED</v>
+      </c>
+      <c r="I11" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>JPN</v>
+      </c>
+      <c r="J11" s="5">
+        <v>2</v>
+      </c>
+      <c r="K11" s="5">
+        <v>2</v>
+      </c>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D12" s="4">
-        <v>46187.833333333328</v>
+        <v>46187.958333333328</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F12" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>NED</v>
+        <v>CIV</v>
       </c>
       <c r="G12" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>JPN</v>
-      </c>
+        <v>ECU</v>
+      </c>
+      <c r="H12" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>CIV</v>
+      </c>
+      <c r="I12" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>ECU</v>
+      </c>
+      <c r="J12" s="5">
+        <v>1</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13">
@@ -1940,108 +2140,193 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>TUN</v>
       </c>
+      <c r="H13" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>SWE</v>
+      </c>
+      <c r="I13" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>TUN</v>
+      </c>
+      <c r="J13" s="5">
+        <v>5</v>
+      </c>
+      <c r="K13" s="5">
+        <v>1</v>
+      </c>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D14" s="4">
-        <v>46188.916666666664</v>
+        <v>46188.666666666664</v>
       </c>
       <c r="E14">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F14" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>KSA</v>
+        <v>ESP</v>
       </c>
       <c r="G14" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>URU</v>
-      </c>
+        <v>CPV</v>
+      </c>
+      <c r="H14" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>ESP</v>
+      </c>
+      <c r="I14" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>CPV</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D15" s="4">
-        <v>46188.666666666664</v>
+        <v>46188.791666666664</v>
       </c>
       <c r="E15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F15" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>ESP</v>
+        <v>BEL</v>
       </c>
       <c r="G15" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>CPV</v>
-      </c>
+        <v>EGY</v>
+      </c>
+      <c r="H15" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>BEL</v>
+      </c>
+      <c r="I15" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>EGY</v>
+      </c>
+      <c r="J15" s="5">
+        <v>1</v>
+      </c>
+      <c r="K15" s="5">
+        <v>1</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="4">
+        <v>46188.916666666664</v>
+      </c>
+      <c r="E16">
+        <v>13</v>
+      </c>
+      <c r="F16" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>KSA</v>
+      </c>
+      <c r="G16" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>URU</v>
+      </c>
+      <c r="H16" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>KSA</v>
+      </c>
+      <c r="I16" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>URU</v>
+      </c>
+      <c r="J16" s="5">
+        <v>1</v>
+      </c>
+      <c r="K16" s="5">
+        <v>1</v>
+      </c>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>24</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D17" s="4">
         <v>46189.041666666664</v>
       </c>
-      <c r="E16">
+      <c r="E17">
         <v>8</v>
       </c>
-      <c r="F16" t="str">
+      <c r="F17" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v>IRN</v>
       </c>
-      <c r="G16" t="str">
+      <c r="G17" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>NZL</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" s="4">
-        <v>46188.791666666664</v>
-      </c>
-      <c r="E17">
-        <v>10</v>
-      </c>
-      <c r="F17" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>BEL</v>
-      </c>
-      <c r="G17" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>EGY</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H17" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>IRN</v>
+      </c>
+      <c r="I17" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>NZL</v>
+      </c>
+      <c r="J17" s="5">
+        <v>2</v>
+      </c>
+      <c r="K17" s="5">
+        <v>2</v>
+      </c>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2065,8 +2350,25 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>SEN</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H18" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>FRA</v>
+      </c>
+      <c r="I18" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>SEN</v>
+      </c>
+      <c r="J18" s="5">
+        <v>3</v>
+      </c>
+      <c r="K18" s="5">
+        <v>1</v>
+      </c>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2090,8 +2392,25 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>NOR</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H19" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>IRQ</v>
+      </c>
+      <c r="I19" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>NOR</v>
+      </c>
+      <c r="J19" s="5">
+        <v>1</v>
+      </c>
+      <c r="K19" s="5">
+        <v>4</v>
+      </c>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2115,8 +2434,25 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>ALG</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H20" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>ARG</v>
+      </c>
+      <c r="I20" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>ALG</v>
+      </c>
+      <c r="J20" s="5">
+        <v>3</v>
+      </c>
+      <c r="K20" s="5">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2140,33 +2476,67 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>JOR</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H21" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>AUT</v>
+      </c>
+      <c r="I21" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>JOR</v>
+      </c>
+      <c r="J21" s="5">
+        <v>3</v>
+      </c>
+      <c r="K21" s="5">
+        <v>1</v>
+      </c>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D22" s="4">
-        <v>46190.958333333328</v>
+        <v>46190.708333333328</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F22" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>GHA</v>
+        <v>POR</v>
       </c>
       <c r="G22" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>PAN</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+        <v>COD</v>
+      </c>
+      <c r="H22" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>POR</v>
+      </c>
+      <c r="I22" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>COD</v>
+      </c>
+      <c r="J22" s="5">
+        <v>1</v>
+      </c>
+      <c r="K22" s="5">
+        <v>1</v>
+      </c>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2190,33 +2560,67 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>CRO</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H23" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>ENG</v>
+      </c>
+      <c r="I23" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>CRO</v>
+      </c>
+      <c r="J23" s="5">
+        <v>4</v>
+      </c>
+      <c r="K23" s="5">
+        <v>2</v>
+      </c>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D24" s="4">
-        <v>46190.708333333328</v>
+        <v>46190.958333333328</v>
       </c>
       <c r="E24">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F24" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>POR</v>
+        <v>GHA</v>
       </c>
       <c r="G24" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>COD</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+        <v>PAN</v>
+      </c>
+      <c r="H24" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>GHA</v>
+      </c>
+      <c r="I24" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>PAN</v>
+      </c>
+      <c r="J24" s="5">
+        <v>1</v>
+      </c>
+      <c r="K24" s="5">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2240,8 +2644,25 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>COL</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H25" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>UZB</v>
+      </c>
+      <c r="I25" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>COL</v>
+      </c>
+      <c r="J25" s="5">
+        <v>1</v>
+      </c>
+      <c r="K25" s="5">
+        <v>3</v>
+      </c>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2265,8 +2686,25 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>RSA</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H26" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>CZE</v>
+      </c>
+      <c r="I26" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>RSA</v>
+      </c>
+      <c r="J26" s="5">
+        <v>1</v>
+      </c>
+      <c r="K26" s="5">
+        <v>1</v>
+      </c>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2290,8 +2728,25 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>BIH</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H27" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>SUI</v>
+      </c>
+      <c r="I27" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>BIH</v>
+      </c>
+      <c r="J27" s="5">
+        <v>4</v>
+      </c>
+      <c r="K27" s="5">
+        <v>1</v>
+      </c>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2315,8 +2770,25 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>QAT</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H28" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>CAN</v>
+      </c>
+      <c r="I28" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>QAT</v>
+      </c>
+      <c r="J28" s="5">
+        <v>6</v>
+      </c>
+      <c r="K28" s="5">
+        <v>0</v>
+      </c>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2340,33 +2812,67 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>KOR</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H29" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>MEX</v>
+      </c>
+      <c r="I29" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>KOR</v>
+      </c>
+      <c r="J29" s="5">
+        <v>1</v>
+      </c>
+      <c r="K29" s="5">
+        <v>0</v>
+      </c>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D30" s="4">
-        <v>46193.020833333336</v>
+        <v>46192.791666666664</v>
       </c>
       <c r="E30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F30" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>BRA</v>
+        <v>USA</v>
       </c>
       <c r="G30" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>HAI</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+        <v>AUS</v>
+      </c>
+      <c r="H30" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>USA</v>
+      </c>
+      <c r="I30" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>AUS</v>
+      </c>
+      <c r="J30" s="5">
+        <v>2</v>
+      </c>
+      <c r="K30" s="5">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2390,133 +2896,235 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>MAR</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H31" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>SCO</v>
+      </c>
+      <c r="I31" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="J31" s="5">
+        <v>0</v>
+      </c>
+      <c r="K31" s="5">
+        <v>1</v>
+      </c>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="4">
+        <v>46193.020833333336</v>
+      </c>
+      <c r="E32">
+        <v>9</v>
+      </c>
+      <c r="F32" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>BRA</v>
+      </c>
+      <c r="G32" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>HAI</v>
+      </c>
+      <c r="H32" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>BRA</v>
+      </c>
+      <c r="I32" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>HAI</v>
+      </c>
+      <c r="J32" s="5">
+        <v>3</v>
+      </c>
+      <c r="K32" s="5">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A33">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" t="s">
         <v>11</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C33" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D33" s="4">
         <v>46193.125</v>
       </c>
-      <c r="E32">
+      <c r="E33">
         <v>11</v>
       </c>
-      <c r="F32" t="str">
+      <c r="F33" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v>TUR</v>
       </c>
-      <c r="G32" t="str">
+      <c r="G33" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>PAR</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="4">
-        <v>46192.791666666664</v>
-      </c>
-      <c r="E33">
-        <v>10</v>
-      </c>
-      <c r="F33" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>USA</v>
-      </c>
-      <c r="G33" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>AUS</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H33" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>TUR</v>
+      </c>
+      <c r="I33" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>PAR</v>
+      </c>
+      <c r="J33" s="5">
+        <v>0</v>
+      </c>
+      <c r="K33" s="5">
+        <v>1</v>
+      </c>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34">
+        <v>35</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" s="4">
+        <v>46193.708333333328</v>
+      </c>
+      <c r="E34">
+        <v>6</v>
+      </c>
+      <c r="F34" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>NED</v>
+      </c>
+      <c r="G34" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>SWE</v>
+      </c>
+      <c r="H34" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>NED</v>
+      </c>
+      <c r="I34" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>SWE</v>
+      </c>
+      <c r="J34" s="5">
+        <v>5</v>
+      </c>
+      <c r="K34" s="5">
+        <v>1</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A35">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>18</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C35" t="s">
         <v>20</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D35" s="4">
         <v>46193.833333333328</v>
       </c>
-      <c r="E34">
+      <c r="E35">
         <v>2</v>
       </c>
-      <c r="F34" t="str">
+      <c r="F35" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v>GER</v>
       </c>
-      <c r="G34" t="str">
+      <c r="G35" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>CIV</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35">
+      <c r="H35" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>GER</v>
+      </c>
+      <c r="I35" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>CIV</v>
+      </c>
+      <c r="J35" s="5">
+        <v>2</v>
+      </c>
+      <c r="K35" s="5">
+        <v>1</v>
+      </c>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A36">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B36" t="s">
         <v>21</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C36" t="s">
         <v>19</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D36" s="4">
         <v>46194</v>
       </c>
-      <c r="E35">
+      <c r="E36">
         <v>4</v>
       </c>
-      <c r="F35" t="str">
+      <c r="F36" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v>ECU</v>
       </c>
-      <c r="G35" t="str">
+      <c r="G36" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>CUW</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="s">
-        <v>22</v>
-      </c>
-      <c r="D36" s="4">
-        <v>46193.708333333328</v>
-      </c>
-      <c r="E36">
-        <v>6</v>
-      </c>
-      <c r="F36" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>NED</v>
-      </c>
-      <c r="G36" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>SWE</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H36" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>ECU</v>
+      </c>
+      <c r="I36" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>CUW</v>
+      </c>
+      <c r="J36" s="5">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2540,83 +3148,151 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>JPN</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H37" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>TUN</v>
+      </c>
+      <c r="I37" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>JPN</v>
+      </c>
+      <c r="J37" s="5">
+        <v>0</v>
+      </c>
+      <c r="K37" s="5">
+        <v>4</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38">
+        <v>38</v>
+      </c>
+      <c r="B38" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" s="4">
+        <v>46194.666666666664</v>
+      </c>
+      <c r="E38">
+        <v>7</v>
+      </c>
+      <c r="F38" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>ESP</v>
+      </c>
+      <c r="G38" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>KSA</v>
+      </c>
+      <c r="H38" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>ESP</v>
+      </c>
+      <c r="I38" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>KSA</v>
+      </c>
+      <c r="J38" s="5">
+        <v>4</v>
+      </c>
+      <c r="K38" s="5">
+        <v>0</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>39</v>
+      </c>
+      <c r="B39" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" s="4">
+        <v>46194.791666666664</v>
+      </c>
+      <c r="E39">
+        <v>8</v>
+      </c>
+      <c r="F39" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>BEL</v>
+      </c>
+      <c r="G39" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>IRN</v>
+      </c>
+      <c r="H39" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>BEL</v>
+      </c>
+      <c r="I39" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>IRN</v>
+      </c>
+      <c r="J39" s="5">
+        <v>0</v>
+      </c>
+      <c r="K39" s="5">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A40">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B40" t="s">
         <v>27</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C40" t="s">
         <v>29</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D40" s="4">
         <v>46194.916666666664</v>
       </c>
-      <c r="E38">
+      <c r="E40">
         <v>13</v>
       </c>
-      <c r="F38" t="str">
+      <c r="F40" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v>URU</v>
       </c>
-      <c r="G38" t="str">
+      <c r="G40" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>CPV</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="s">
-        <v>28</v>
-      </c>
-      <c r="C39" t="s">
-        <v>26</v>
-      </c>
-      <c r="D39" s="4">
-        <v>46194.666666666664</v>
-      </c>
-      <c r="E39">
-        <v>7</v>
-      </c>
-      <c r="F39" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>ESP</v>
-      </c>
-      <c r="G39" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>KSA</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="s">
-        <v>30</v>
-      </c>
-      <c r="C40" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" s="4">
-        <v>46194.791666666664</v>
-      </c>
-      <c r="E40">
-        <v>8</v>
-      </c>
-      <c r="F40" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>BEL</v>
-      </c>
-      <c r="G40" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>IRN</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H40" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>URU</v>
+      </c>
+      <c r="I40" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>CPV</v>
+      </c>
+      <c r="J40" s="5">
+        <v>2</v>
+      </c>
+      <c r="K40" s="5">
+        <v>2</v>
+      </c>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2640,33 +3316,67 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>EGY</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H41" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>NZL</v>
+      </c>
+      <c r="I41" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>EGY</v>
+      </c>
+      <c r="J41" s="5">
+        <v>1</v>
+      </c>
+      <c r="K41" s="5">
+        <v>3</v>
+      </c>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C42" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D42" s="4">
-        <v>46196</v>
+        <v>46195.708333333328</v>
       </c>
       <c r="E42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F42" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>NOR</v>
+        <v>ARG</v>
       </c>
       <c r="G42" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>SEN</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+        <v>AUT</v>
+      </c>
+      <c r="H42" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>ARG</v>
+      </c>
+      <c r="I42" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>AUT</v>
+      </c>
+      <c r="J42" s="5">
+        <v>2</v>
+      </c>
+      <c r="K42" s="5">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2690,33 +3400,67 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>IRQ</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H43" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>FRA</v>
+      </c>
+      <c r="I43" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>IRQ</v>
+      </c>
+      <c r="J43" s="5">
+        <v>3</v>
+      </c>
+      <c r="K43" s="5">
+        <v>0</v>
+      </c>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C44" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D44" s="4">
-        <v>46195.708333333328</v>
+        <v>46196</v>
       </c>
       <c r="E44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F44" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>ARG</v>
+        <v>NOR</v>
       </c>
       <c r="G44" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>AUT</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+        <v>SEN</v>
+      </c>
+      <c r="H44" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>NOR</v>
+      </c>
+      <c r="I44" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>SEN</v>
+      </c>
+      <c r="J44" s="5">
+        <v>3</v>
+      </c>
+      <c r="K44" s="5">
+        <v>2</v>
+      </c>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2740,83 +3484,151 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>ALG</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H45" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>JOR</v>
+      </c>
+      <c r="I45" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>ALG</v>
+      </c>
+      <c r="J45" s="5">
+        <v>1</v>
+      </c>
+      <c r="K45" s="5">
+        <v>2</v>
+      </c>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46">
+        <v>47</v>
+      </c>
+      <c r="B46" t="s">
+        <v>103</v>
+      </c>
+      <c r="C46" t="s">
+        <v>105</v>
+      </c>
+      <c r="D46" s="4">
+        <v>46196.708333333328</v>
+      </c>
+      <c r="E46">
+        <v>6</v>
+      </c>
+      <c r="F46" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>POR</v>
+      </c>
+      <c r="G46" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>UZB</v>
+      </c>
+      <c r="H46" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>POR</v>
+      </c>
+      <c r="I46" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>UZB</v>
+      </c>
+      <c r="J46" s="5">
+        <v>5</v>
+      </c>
+      <c r="K46" s="5">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A47">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>107</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C47" t="s">
         <v>109</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D47" s="4">
         <v>46196.833333333328</v>
       </c>
-      <c r="E46">
+      <c r="E47">
         <v>12</v>
       </c>
-      <c r="F46" t="str">
+      <c r="F47" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v>ENG</v>
       </c>
-      <c r="G46" t="str">
+      <c r="G47" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>GHA</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47">
+      <c r="H47" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>ENG</v>
+      </c>
+      <c r="I47" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>GHA</v>
+      </c>
+      <c r="J47" s="5">
+        <v>0</v>
+      </c>
+      <c r="K47" s="5">
+        <v>0</v>
+      </c>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A48">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B48" t="s">
         <v>110</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C48" t="s">
         <v>108</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D48" s="4">
         <v>46196.958333333328</v>
       </c>
-      <c r="E47">
+      <c r="E48">
         <v>2</v>
       </c>
-      <c r="F47" t="str">
+      <c r="F48" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v>PAN</v>
       </c>
-      <c r="G47" t="str">
+      <c r="G48" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>CRO</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="s">
-        <v>103</v>
-      </c>
-      <c r="C48" t="s">
-        <v>105</v>
-      </c>
-      <c r="D48" s="4">
-        <v>46196.708333333328</v>
-      </c>
-      <c r="E48">
-        <v>6</v>
-      </c>
-      <c r="F48" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>POR</v>
-      </c>
-      <c r="G48" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>UZB</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H48" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>PAN</v>
+      </c>
+      <c r="I48" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>CRO</v>
+      </c>
+      <c r="J48" s="5">
+        <v>0</v>
+      </c>
+      <c r="K48" s="5">
+        <v>1</v>
+      </c>
+      <c r="L48" s="5"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2840,108 +3652,193 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>COD</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H49" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>COL</v>
+      </c>
+      <c r="I49" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>COD</v>
+      </c>
+      <c r="J49" s="5">
+        <v>1</v>
+      </c>
+      <c r="K49" s="5">
+        <v>0</v>
+      </c>
+      <c r="L49" s="5"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50">
+        <v>51</v>
+      </c>
+      <c r="B50" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" s="4">
+        <v>46197.791666666664</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>SUI</v>
+      </c>
+      <c r="G50" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>CAN</v>
+      </c>
+      <c r="H50" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>SUI</v>
+      </c>
+      <c r="I50" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>CAN</v>
+      </c>
+      <c r="J50" s="5">
+        <v>2</v>
+      </c>
+      <c r="K50" s="5">
+        <v>1</v>
+      </c>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>52</v>
+      </c>
+      <c r="B51" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="4">
+        <v>46197.791666666664</v>
+      </c>
+      <c r="E51">
+        <v>10</v>
+      </c>
+      <c r="F51" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>BIH</v>
+      </c>
+      <c r="G51" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>QAT</v>
+      </c>
+      <c r="H51" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>BIH</v>
+      </c>
+      <c r="I51" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>QAT</v>
+      </c>
+      <c r="J51" s="5">
+        <v>3</v>
+      </c>
+      <c r="K51" s="5">
+        <v>1</v>
+      </c>
+      <c r="L51" s="5"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A52">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B52" t="s">
         <v>13</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C52" t="s">
         <v>14</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D52" s="4">
         <v>46197.916666666664</v>
       </c>
-      <c r="E50">
+      <c r="E52">
         <v>13</v>
       </c>
-      <c r="F50" t="str">
+      <c r="F52" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v>SCO</v>
       </c>
-      <c r="G50" t="str">
+      <c r="G52" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>BRA</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51">
+      <c r="H52" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>SCO</v>
+      </c>
+      <c r="I52" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>BRA</v>
+      </c>
+      <c r="J52" s="5">
+        <v>0</v>
+      </c>
+      <c r="K52" s="5">
+        <v>3</v>
+      </c>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A53">
         <v>50</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B53" t="s">
         <v>15</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C53" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D53" s="4">
         <v>46197.916666666664</v>
       </c>
-      <c r="E51">
+      <c r="E53">
         <v>7</v>
       </c>
-      <c r="F51" t="str">
+      <c r="F53" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v>MAR</v>
       </c>
-      <c r="G51" t="str">
+      <c r="G53" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>HAI</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="H53" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>MAR</v>
+      </c>
+      <c r="I53" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>HAI</v>
+      </c>
+      <c r="J53" s="5">
         <v>4</v>
       </c>
-      <c r="D52" s="4">
-        <v>46197.791666666664</v>
-      </c>
-      <c r="E52">
-        <v>1</v>
-      </c>
-      <c r="F52" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>SUI</v>
-      </c>
-      <c r="G52" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>CAN</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="s">
-        <v>5</v>
-      </c>
-      <c r="C53" t="s">
-        <v>6</v>
-      </c>
-      <c r="D53" s="4">
-        <v>46197.791666666664</v>
-      </c>
-      <c r="E53">
-        <v>10</v>
-      </c>
-      <c r="F53" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>BIH</v>
-      </c>
-      <c r="G53" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>QAT</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="K53" s="5">
+        <v>2</v>
+      </c>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2965,8 +3862,25 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>MEX</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H54" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>CZE</v>
+      </c>
+      <c r="I54" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>MEX</v>
+      </c>
+      <c r="J54" s="5">
+        <v>0</v>
+      </c>
+      <c r="K54" s="5">
+        <v>3</v>
+      </c>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2990,8 +3904,25 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>KOR</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H55" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>RSA</v>
+      </c>
+      <c r="I55" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>KOR</v>
+      </c>
+      <c r="J55" s="5">
+        <v>1</v>
+      </c>
+      <c r="K55" s="5">
+        <v>0</v>
+      </c>
+      <c r="L55" s="5"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3015,8 +3946,25 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>CIV</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H56" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>CUW</v>
+      </c>
+      <c r="I56" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>CIV</v>
+      </c>
+      <c r="J56" s="5">
+        <v>0</v>
+      </c>
+      <c r="K56" s="5">
+        <v>2</v>
+      </c>
+      <c r="L56" s="5"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="5"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3040,8 +3988,25 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>GER</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H57" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>ECU</v>
+      </c>
+      <c r="I57" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>GER</v>
+      </c>
+      <c r="J57" s="5">
+        <v>2</v>
+      </c>
+      <c r="K57" s="5">
+        <v>1</v>
+      </c>
+      <c r="L57" s="5"/>
+      <c r="M57" s="5"/>
+      <c r="N57" s="5"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3065,8 +4030,25 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>SWE</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H58" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>JPN</v>
+      </c>
+      <c r="I58" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>SWE</v>
+      </c>
+      <c r="J58" s="5">
+        <v>1</v>
+      </c>
+      <c r="K58" s="5">
+        <v>1</v>
+      </c>
+      <c r="L58" s="5"/>
+      <c r="M58" s="5"/>
+      <c r="N58" s="5"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3090,8 +4072,25 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>NED</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H59" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>TUN</v>
+      </c>
+      <c r="I59" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>NED</v>
+      </c>
+      <c r="J59" s="5">
+        <v>1</v>
+      </c>
+      <c r="K59" s="5">
+        <v>3</v>
+      </c>
+      <c r="L59" s="5"/>
+      <c r="M59" s="5"/>
+      <c r="N59" s="5"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3115,8 +4114,25 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>USA</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H60" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>TUR</v>
+      </c>
+      <c r="I60" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>USA</v>
+      </c>
+      <c r="J60" s="5">
+        <v>3</v>
+      </c>
+      <c r="K60" s="5">
+        <v>2</v>
+      </c>
+      <c r="L60" s="5"/>
+      <c r="M60" s="5"/>
+      <c r="N60" s="5"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3140,8 +4156,25 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>AUS</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H61" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>PAR</v>
+      </c>
+      <c r="I61" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>AUS</v>
+      </c>
+      <c r="J61" s="5">
+        <v>0</v>
+      </c>
+      <c r="K61" s="5">
+        <v>0</v>
+      </c>
+      <c r="L61" s="5"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3165,8 +4198,25 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>FRA</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H62" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>NOR</v>
+      </c>
+      <c r="I62" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>FRA</v>
+      </c>
+      <c r="J62" s="5">
+        <v>1</v>
+      </c>
+      <c r="K62" s="5">
+        <v>4</v>
+      </c>
+      <c r="L62" s="5"/>
+      <c r="M62" s="5"/>
+      <c r="N62" s="5"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3190,108 +4240,193 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>IRQ</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H63" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>SEN</v>
+      </c>
+      <c r="I63" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>IRQ</v>
+      </c>
+      <c r="J63" s="5">
+        <v>5</v>
+      </c>
+      <c r="K63" s="5">
+        <v>0</v>
+      </c>
+      <c r="L63" s="5"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="5"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64">
+        <v>65</v>
+      </c>
+      <c r="B64" t="s">
+        <v>29</v>
+      </c>
+      <c r="C64" t="s">
+        <v>26</v>
+      </c>
+      <c r="D64" s="4">
+        <v>46200</v>
+      </c>
+      <c r="E64">
+        <v>6</v>
+      </c>
+      <c r="F64" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>CPV</v>
+      </c>
+      <c r="G64" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>KSA</v>
+      </c>
+      <c r="H64" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>CPV</v>
+      </c>
+      <c r="I64" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>KSA</v>
+      </c>
+      <c r="J64" s="5">
+        <v>0</v>
+      </c>
+      <c r="K64" s="5">
+        <v>0</v>
+      </c>
+      <c r="L64" s="5"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="5"/>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>66</v>
+      </c>
+      <c r="B65" t="s">
+        <v>27</v>
+      </c>
+      <c r="C65" t="s">
+        <v>28</v>
+      </c>
+      <c r="D65" s="4">
+        <v>46200</v>
+      </c>
+      <c r="E65">
+        <v>15</v>
+      </c>
+      <c r="F65" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>URU</v>
+      </c>
+      <c r="G65" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>ESP</v>
+      </c>
+      <c r="H65" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>URU</v>
+      </c>
+      <c r="I65" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>ESP</v>
+      </c>
+      <c r="J65" s="5">
+        <v>0</v>
+      </c>
+      <c r="K65" s="5">
+        <v>1</v>
+      </c>
+      <c r="L65" s="5"/>
+      <c r="M65" s="5"/>
+      <c r="N65" s="5"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A66">
         <v>63</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B66" t="s">
         <v>31</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C66" t="s">
         <v>24</v>
       </c>
-      <c r="D64" s="4">
+      <c r="D66" s="4">
         <v>46200.125</v>
       </c>
-      <c r="E64">
+      <c r="E66">
         <v>10</v>
       </c>
-      <c r="F64" t="str">
+      <c r="F66" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v>EGY</v>
       </c>
-      <c r="G64" t="str">
+      <c r="G66" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>IRN</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A65">
+      <c r="H66" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>EGY</v>
+      </c>
+      <c r="I66" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>IRN</v>
+      </c>
+      <c r="J66" s="5">
+        <v>1</v>
+      </c>
+      <c r="K66" s="5">
+        <v>1</v>
+      </c>
+      <c r="L66" s="5"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="5"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A67">
         <v>64</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B67" t="s">
         <v>25</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C67" t="s">
         <v>30</v>
       </c>
-      <c r="D65" s="4">
+      <c r="D67" s="4">
         <v>46200.125</v>
       </c>
-      <c r="E65">
-        <v>1</v>
-      </c>
-      <c r="F65" t="str">
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v>NZL</v>
       </c>
-      <c r="G65" t="str">
+      <c r="G67" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>BEL</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="s">
-        <v>29</v>
-      </c>
-      <c r="C66" t="s">
-        <v>26</v>
-      </c>
-      <c r="D66" s="4">
-        <v>46200</v>
-      </c>
-      <c r="E66">
-        <v>6</v>
-      </c>
-      <c r="F66" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>CPV</v>
-      </c>
-      <c r="G66" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>KSA</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="s">
-        <v>27</v>
-      </c>
-      <c r="C67" t="s">
-        <v>28</v>
-      </c>
-      <c r="D67" s="4">
-        <v>46200</v>
-      </c>
-      <c r="E67">
-        <v>15</v>
-      </c>
-      <c r="F67" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>URU</v>
-      </c>
-      <c r="G67" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>ESP</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H67" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>NZL</v>
+      </c>
+      <c r="I67" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>BEL</v>
+      </c>
+      <c r="J67" s="5">
+        <v>1</v>
+      </c>
+      <c r="K67" s="5">
+        <v>5</v>
+      </c>
+      <c r="L67" s="5"/>
+      <c r="M67" s="5"/>
+      <c r="N67" s="5"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3315,8 +4450,25 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>ENG</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H68" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>PAN</v>
+      </c>
+      <c r="I68" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>ENG</v>
+      </c>
+      <c r="J68" s="5">
+        <v>0</v>
+      </c>
+      <c r="K68" s="5">
+        <v>2</v>
+      </c>
+      <c r="L68" s="5"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3340,108 +4492,193 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>GHA</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H69" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>CRO</v>
+      </c>
+      <c r="I69" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>GHA</v>
+      </c>
+      <c r="J69" s="5">
+        <v>2</v>
+      </c>
+      <c r="K69" s="5">
+        <v>1</v>
+      </c>
+      <c r="L69" s="5"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70">
+        <v>71</v>
+      </c>
+      <c r="B70" t="s">
+        <v>106</v>
+      </c>
+      <c r="C70" t="s">
+        <v>103</v>
+      </c>
+      <c r="D70" s="4">
+        <v>46200.979166666664</v>
+      </c>
+      <c r="E70">
+        <v>13</v>
+      </c>
+      <c r="F70" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>COL</v>
+      </c>
+      <c r="G70" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>POR</v>
+      </c>
+      <c r="H70" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>COL</v>
+      </c>
+      <c r="I70" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>POR</v>
+      </c>
+      <c r="J70" s="5">
+        <v>0</v>
+      </c>
+      <c r="K70" s="5">
+        <v>0</v>
+      </c>
+      <c r="L70" s="5"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="5"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>72</v>
+      </c>
+      <c r="B71" t="s">
+        <v>104</v>
+      </c>
+      <c r="C71" t="s">
+        <v>105</v>
+      </c>
+      <c r="D71" s="4">
+        <v>46200.979166666664</v>
+      </c>
+      <c r="E71">
+        <v>7</v>
+      </c>
+      <c r="F71" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>COD</v>
+      </c>
+      <c r="G71" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>UZB</v>
+      </c>
+      <c r="H71" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>COD</v>
+      </c>
+      <c r="I71" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>UZB</v>
+      </c>
+      <c r="J71" s="5">
+        <v>3</v>
+      </c>
+      <c r="K71" s="5">
+        <v>1</v>
+      </c>
+      <c r="L71" s="5"/>
+      <c r="M71" s="5"/>
+      <c r="N71" s="5"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A72">
         <v>69</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B72" t="s">
         <v>100</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C72" t="s">
         <v>101</v>
       </c>
-      <c r="D70" s="4">
+      <c r="D72" s="4">
         <v>46201.083333333328</v>
       </c>
-      <c r="E70">
+      <c r="E72">
         <v>4</v>
       </c>
-      <c r="F70" t="str">
+      <c r="F72" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v>ALG</v>
       </c>
-      <c r="G70" t="str">
+      <c r="G72" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>AUT</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A71">
+      <c r="H72" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>ALG</v>
+      </c>
+      <c r="I72" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>AUT</v>
+      </c>
+      <c r="J72" s="5">
+        <v>3</v>
+      </c>
+      <c r="K72" s="5">
+        <v>3</v>
+      </c>
+      <c r="L72" s="5"/>
+      <c r="M72" s="5"/>
+      <c r="N72" s="5"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A73">
         <v>70</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B73" t="s">
         <v>102</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C73" t="s">
         <v>99</v>
       </c>
-      <c r="D71" s="4">
+      <c r="D73" s="4">
         <v>46201.083333333328</v>
       </c>
-      <c r="E71">
+      <c r="E73">
         <v>5</v>
       </c>
-      <c r="F71" t="str">
+      <c r="F73" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v>JOR</v>
       </c>
-      <c r="G71" t="str">
+      <c r="G73" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v>ARG</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" t="s">
-        <v>106</v>
-      </c>
-      <c r="C72" t="s">
-        <v>103</v>
-      </c>
-      <c r="D72" s="4">
-        <v>46200.979166666664</v>
-      </c>
-      <c r="E72">
-        <v>13</v>
-      </c>
-      <c r="F72" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>COL</v>
-      </c>
-      <c r="G72" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>POR</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" t="s">
-        <v>104</v>
-      </c>
-      <c r="C73" t="s">
-        <v>105</v>
-      </c>
-      <c r="D73" s="4">
-        <v>46200.979166666664</v>
-      </c>
-      <c r="E73">
-        <v>7</v>
-      </c>
-      <c r="F73" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v>COD</v>
-      </c>
-      <c r="G73" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v>UZB</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H73" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v>JOR</v>
+      </c>
+      <c r="I73" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v>ARG</v>
+      </c>
+      <c r="J73" s="5">
+        <v>1</v>
+      </c>
+      <c r="K73" s="5">
+        <v>3</v>
+      </c>
+      <c r="L73" s="5"/>
+      <c r="M73" s="5"/>
+      <c r="N73" s="5"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -3465,133 +4702,235 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H74" t="s">
+        <v>226</v>
+      </c>
+      <c r="I74" t="s">
+        <v>74</v>
+      </c>
+      <c r="J74" s="5">
+        <v>0</v>
+      </c>
+      <c r="K74" s="5">
+        <v>1</v>
+      </c>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="5"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75">
+        <v>76</v>
+      </c>
+      <c r="B75" t="s">
+        <v>34</v>
+      </c>
+      <c r="C75" t="s">
+        <v>41</v>
+      </c>
+      <c r="D75" s="4">
+        <v>46202.708333333328</v>
+      </c>
+      <c r="E75">
+        <v>6</v>
+      </c>
+      <c r="F75" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v/>
+      </c>
+      <c r="H75" t="s">
+        <v>91</v>
+      </c>
+      <c r="I75" t="s">
+        <v>90</v>
+      </c>
+      <c r="J75" s="5">
+        <v>2</v>
+      </c>
+      <c r="K75" s="5">
+        <v>1</v>
+      </c>
+      <c r="L75" s="5"/>
+      <c r="M75" s="5"/>
+      <c r="N75" s="5"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A76">
         <v>74</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B76" t="s">
         <v>40</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C76" t="s">
         <v>243</v>
       </c>
-      <c r="D75" s="4">
+      <c r="D76" s="4">
         <v>46202.854166666664</v>
       </c>
-      <c r="E75">
+      <c r="E76">
         <v>12</v>
       </c>
-      <c r="F75" t="str">
+      <c r="F76" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-      <c r="G75" t="str">
+      <c r="G76" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A76">
+      <c r="H76" t="s">
+        <v>89</v>
+      </c>
+      <c r="I76" t="s">
+        <v>161</v>
+      </c>
+      <c r="J76" s="5">
+        <v>1</v>
+      </c>
+      <c r="K76" s="5">
+        <v>1</v>
+      </c>
+      <c r="L76" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M76" s="5">
+        <v>3</v>
+      </c>
+      <c r="N76" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A77">
         <v>75</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B77" t="s">
         <v>44</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C77" t="s">
         <v>39</v>
       </c>
-      <c r="D76" s="4">
+      <c r="D77" s="4">
         <v>46203.041666666664</v>
       </c>
-      <c r="E76">
+      <c r="E77">
         <v>16</v>
       </c>
-      <c r="F76" t="str">
+      <c r="F77" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-      <c r="G76" t="str">
+      <c r="G77" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A77">
-        <v>76</v>
-      </c>
-      <c r="B77" t="s">
-        <v>34</v>
-      </c>
-      <c r="C77" t="s">
-        <v>41</v>
-      </c>
-      <c r="D77" s="4">
-        <v>46202.708333333328</v>
-      </c>
-      <c r="E77">
-        <v>6</v>
-      </c>
-      <c r="F77" t="str">
+      <c r="H77" t="s">
+        <v>77</v>
+      </c>
+      <c r="I77" t="s">
+        <v>82</v>
+      </c>
+      <c r="J77" s="5">
+        <v>1</v>
+      </c>
+      <c r="K77" s="5">
+        <v>1</v>
+      </c>
+      <c r="L77" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M77" s="5">
+        <v>2</v>
+      </c>
+      <c r="N77" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>78</v>
+      </c>
+      <c r="B78" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" t="s">
+        <v>123</v>
+      </c>
+      <c r="D78" s="4">
+        <v>46203.708333333328</v>
+      </c>
+      <c r="E78">
+        <v>5</v>
+      </c>
+      <c r="F78" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-      <c r="G77" t="str">
+      <c r="G78" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A78">
+      <c r="H78" t="s">
+        <v>163</v>
+      </c>
+      <c r="I78" t="s">
+        <v>111</v>
+      </c>
+      <c r="J78" s="5">
+        <v>1</v>
+      </c>
+      <c r="K78" s="5">
+        <v>2</v>
+      </c>
+      <c r="L78" s="5"/>
+      <c r="M78" s="5"/>
+      <c r="N78" s="5"/>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A79">
         <v>77</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B79" t="s">
         <v>122</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C79" t="s">
         <v>244</v>
       </c>
-      <c r="D78" s="4">
+      <c r="D79" s="4">
         <v>46203.875</v>
       </c>
-      <c r="E78">
+      <c r="E79">
         <v>3</v>
       </c>
-      <c r="F78" t="str">
+      <c r="F79" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-      <c r="G78" t="str">
+      <c r="G79" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A79">
-        <v>78</v>
-      </c>
-      <c r="B79" t="s">
-        <v>45</v>
-      </c>
-      <c r="C79" t="s">
-        <v>123</v>
-      </c>
-      <c r="D79" s="4">
-        <v>46203.708333333328</v>
-      </c>
-      <c r="E79">
-        <v>5</v>
-      </c>
-      <c r="F79" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v/>
-      </c>
-      <c r="G79" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H79" t="s">
+        <v>85</v>
+      </c>
+      <c r="I79" t="s">
+        <v>222</v>
+      </c>
+      <c r="J79" s="5">
+        <v>3</v>
+      </c>
+      <c r="K79" s="5">
+        <v>0</v>
+      </c>
+      <c r="L79" s="5"/>
+      <c r="M79" s="5"/>
+      <c r="N79" s="5"/>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -3615,8 +4954,23 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H80" t="s">
+        <v>73</v>
+      </c>
+      <c r="I80" t="s">
+        <v>75</v>
+      </c>
+      <c r="J80" s="5">
+        <v>2</v>
+      </c>
+      <c r="K80" s="5">
+        <v>0</v>
+      </c>
+      <c r="L80" s="5"/>
+      <c r="M80" s="5"/>
+      <c r="N80" s="5"/>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -3640,108 +4994,185 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H81" t="s">
+        <v>78</v>
+      </c>
+      <c r="I81" t="s">
+        <v>225</v>
+      </c>
+      <c r="J81" s="5">
+        <v>2</v>
+      </c>
+      <c r="K81" s="5">
+        <v>1</v>
+      </c>
+      <c r="L81" s="5"/>
+      <c r="M81" s="5"/>
+      <c r="N81" s="5"/>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82">
+        <v>82</v>
+      </c>
+      <c r="B82" t="s">
+        <v>42</v>
+      </c>
+      <c r="C82" t="s">
+        <v>248</v>
+      </c>
+      <c r="D82" s="4">
+        <v>46204.833333333328</v>
+      </c>
+      <c r="E82">
+        <v>10</v>
+      </c>
+      <c r="F82" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v/>
+      </c>
+      <c r="H82" t="s">
         <v>81</v>
       </c>
-      <c r="B82" t="s">
+      <c r="I82" t="s">
+        <v>76</v>
+      </c>
+      <c r="J82" s="5">
+        <v>3</v>
+      </c>
+      <c r="K82" s="5">
+        <v>2</v>
+      </c>
+      <c r="L82" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M82" s="5"/>
+      <c r="N82" s="5"/>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="B83" t="s">
         <v>38</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C83" t="s">
         <v>247</v>
       </c>
-      <c r="D82" s="4">
+      <c r="D83" s="4">
         <v>46205</v>
       </c>
-      <c r="E82">
+      <c r="E83">
         <v>11</v>
       </c>
-      <c r="F82" t="str">
+      <c r="F83" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-      <c r="G82" t="str">
+      <c r="G83" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A83">
-        <v>82</v>
-      </c>
-      <c r="B83" t="s">
-        <v>42</v>
-      </c>
-      <c r="C83" t="s">
-        <v>248</v>
-      </c>
-      <c r="D83" s="4">
-        <v>46204.833333333328</v>
-      </c>
-      <c r="E83">
-        <v>10</v>
-      </c>
-      <c r="F83" t="str">
+      <c r="H83" t="s">
+        <v>51</v>
+      </c>
+      <c r="I83" t="s">
+        <v>224</v>
+      </c>
+      <c r="J83" s="5">
+        <v>2</v>
+      </c>
+      <c r="K83" s="5">
+        <v>0</v>
+      </c>
+      <c r="L83" s="5"/>
+      <c r="M83" s="5"/>
+      <c r="N83" s="5"/>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>84</v>
+      </c>
+      <c r="B84" t="s">
+        <v>46</v>
+      </c>
+      <c r="C84" t="s">
+        <v>127</v>
+      </c>
+      <c r="D84" s="4">
+        <v>46205.791666666664</v>
+      </c>
+      <c r="E84">
+        <v>8</v>
+      </c>
+      <c r="F84" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-      <c r="G83" t="str">
+      <c r="G84" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A84">
+      <c r="H84" t="s">
+        <v>88</v>
+      </c>
+      <c r="I84" t="s">
+        <v>116</v>
+      </c>
+      <c r="J84" s="5">
+        <v>3</v>
+      </c>
+      <c r="K84" s="5">
+        <v>0</v>
+      </c>
+      <c r="L84" s="5"/>
+      <c r="M84" s="5"/>
+      <c r="N84" s="5"/>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A85">
         <v>83</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B85" t="s">
         <v>125</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C85" t="s">
         <v>126</v>
       </c>
-      <c r="D84" s="4">
+      <c r="D85" s="4">
         <v>46205.958333333328</v>
       </c>
-      <c r="E84">
+      <c r="E85">
         <v>2</v>
       </c>
-      <c r="F84" t="str">
+      <c r="F85" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-      <c r="G84" t="str">
+      <c r="G85" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85" t="s">
-        <v>46</v>
-      </c>
-      <c r="C85" t="s">
-        <v>127</v>
-      </c>
-      <c r="D85" s="4">
-        <v>46205.791666666664</v>
-      </c>
-      <c r="E85">
-        <v>8</v>
-      </c>
-      <c r="F85" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v/>
-      </c>
-      <c r="G85" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H85" t="s">
+        <v>53</v>
+      </c>
+      <c r="I85" t="s">
+        <v>83</v>
+      </c>
+      <c r="J85" s="5">
+        <v>2</v>
+      </c>
+      <c r="K85" s="5">
+        <v>1</v>
+      </c>
+      <c r="L85" s="5"/>
+      <c r="M85" s="5"/>
+      <c r="N85" s="5"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -3765,133 +5196,231 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H86" t="s">
+        <v>92</v>
+      </c>
+      <c r="I86" t="s">
+        <v>113</v>
+      </c>
+      <c r="J86" s="5">
+        <v>2</v>
+      </c>
+      <c r="K86" s="5">
+        <v>0</v>
+      </c>
+      <c r="L86" s="5"/>
+      <c r="M86" s="5"/>
+      <c r="N86" s="5"/>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87">
+        <v>88</v>
+      </c>
+      <c r="B87" t="s">
+        <v>35</v>
+      </c>
+      <c r="C87" t="s">
+        <v>47</v>
+      </c>
+      <c r="D87" s="4">
+        <v>46206.75</v>
+      </c>
+      <c r="E87">
+        <v>5</v>
+      </c>
+      <c r="F87" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
+        <v/>
+      </c>
+      <c r="H87" t="s">
         <v>86</v>
       </c>
-      <c r="B87" t="s">
+      <c r="I87" t="s">
+        <v>112</v>
+      </c>
+      <c r="J87" s="5">
+        <v>1</v>
+      </c>
+      <c r="K87" s="5">
+        <v>1</v>
+      </c>
+      <c r="L87" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M87" s="5">
+        <v>2</v>
+      </c>
+      <c r="N87" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="B88" t="s">
         <v>128</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C88" t="s">
         <v>43</v>
       </c>
-      <c r="D87" s="4">
+      <c r="D88" s="4">
         <v>46206.916666666664</v>
       </c>
-      <c r="E87">
+      <c r="E88">
         <v>13</v>
       </c>
-      <c r="F87" t="str">
+      <c r="F88" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-      <c r="G87" t="str">
+      <c r="G88" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A88">
+      <c r="H88" t="s">
+        <v>80</v>
+      </c>
+      <c r="I88" t="s">
+        <v>165</v>
+      </c>
+      <c r="J88" s="5">
+        <v>3</v>
+      </c>
+      <c r="K88" s="5">
+        <v>2</v>
+      </c>
+      <c r="L88" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M88" s="5"/>
+      <c r="N88" s="5"/>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A89">
         <v>87</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B89" t="s">
         <v>129</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C89" t="s">
         <v>250</v>
       </c>
-      <c r="D88" s="4">
+      <c r="D89" s="4">
         <v>46207.0625</v>
       </c>
-      <c r="E88">
+      <c r="E89">
         <v>4</v>
       </c>
-      <c r="F88" t="str">
+      <c r="F89" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-      <c r="G88" t="str">
+      <c r="G89" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A89">
-        <v>88</v>
-      </c>
-      <c r="B89" t="s">
-        <v>35</v>
-      </c>
-      <c r="C89" t="s">
-        <v>47</v>
-      </c>
-      <c r="D89" s="4">
-        <v>46206.75</v>
-      </c>
-      <c r="E89">
-        <v>5</v>
-      </c>
-      <c r="F89" t="str">
+      <c r="H89" t="s">
+        <v>114</v>
+      </c>
+      <c r="I89" t="s">
+        <v>168</v>
+      </c>
+      <c r="J89" s="5">
+        <v>1</v>
+      </c>
+      <c r="K89" s="5">
+        <v>0</v>
+      </c>
+      <c r="L89" s="5"/>
+      <c r="M89" s="5"/>
+      <c r="N89" s="5"/>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>90</v>
+      </c>
+      <c r="B90" t="s">
+        <v>132</v>
+      </c>
+      <c r="C90" t="s">
+        <v>133</v>
+      </c>
+      <c r="D90" s="4">
+        <v>46207.708333333328</v>
+      </c>
+      <c r="E90">
+        <v>6</v>
+      </c>
+      <c r="F90" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-      <c r="G89" t="str">
+      <c r="G90" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A90">
+      <c r="H90" t="s">
+        <v>74</v>
+      </c>
+      <c r="I90" t="s">
+        <v>82</v>
+      </c>
+      <c r="J90" s="5">
+        <v>0</v>
+      </c>
+      <c r="K90" s="5">
+        <v>3</v>
+      </c>
+      <c r="L90" s="5"/>
+      <c r="M90" s="5"/>
+      <c r="N90" s="5"/>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A91">
         <v>89</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B91" t="s">
         <v>130</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C91" t="s">
         <v>131</v>
       </c>
-      <c r="D90" s="4">
+      <c r="D91" s="4">
         <v>46207.875</v>
       </c>
-      <c r="E90">
+      <c r="E91">
         <v>9</v>
       </c>
-      <c r="F90" t="str">
+      <c r="F91" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-      <c r="G90" t="str">
+      <c r="G91" t="str">
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A91">
-        <v>90</v>
-      </c>
-      <c r="B91" t="s">
-        <v>132</v>
-      </c>
-      <c r="C91" t="s">
-        <v>133</v>
-      </c>
-      <c r="D91" s="4">
-        <v>46207.708333333328</v>
-      </c>
-      <c r="E91">
-        <v>6</v>
-      </c>
-      <c r="F91" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[home-seed]],seeds[seed],0)),"")</f>
-        <v/>
-      </c>
-      <c r="G91" t="str">
-        <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H91" t="s">
+        <v>161</v>
+      </c>
+      <c r="I91" t="s">
+        <v>85</v>
+      </c>
+      <c r="J91" s="5">
+        <v>0</v>
+      </c>
+      <c r="K91" s="5">
+        <v>1</v>
+      </c>
+      <c r="L91" s="5"/>
+      <c r="M91" s="5"/>
+      <c r="N91" s="5"/>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -3915,8 +5444,23 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H92" t="s">
+        <v>91</v>
+      </c>
+      <c r="I92" t="s">
+        <v>111</v>
+      </c>
+      <c r="J92" s="5">
+        <v>1</v>
+      </c>
+      <c r="K92" s="5">
+        <v>2</v>
+      </c>
+      <c r="L92" s="5"/>
+      <c r="M92" s="5"/>
+      <c r="N92" s="5"/>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -3940,8 +5484,23 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H93" t="s">
+        <v>73</v>
+      </c>
+      <c r="I93" t="s">
+        <v>78</v>
+      </c>
+      <c r="J93" s="5">
+        <v>2</v>
+      </c>
+      <c r="K93" s="5">
+        <v>3</v>
+      </c>
+      <c r="L93" s="5"/>
+      <c r="M93" s="5"/>
+      <c r="N93" s="5"/>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -3965,8 +5524,23 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H94" t="s">
+        <v>53</v>
+      </c>
+      <c r="I94" t="s">
+        <v>88</v>
+      </c>
+      <c r="J94" s="5">
+        <v>0</v>
+      </c>
+      <c r="K94" s="5">
+        <v>1</v>
+      </c>
+      <c r="L94" s="5"/>
+      <c r="M94" s="5"/>
+      <c r="N94" s="5"/>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -3990,8 +5564,23 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H95" t="s">
+        <v>51</v>
+      </c>
+      <c r="I95" t="s">
+        <v>81</v>
+      </c>
+      <c r="J95" s="5">
+        <v>1</v>
+      </c>
+      <c r="K95" s="5">
+        <v>4</v>
+      </c>
+      <c r="L95" s="5"/>
+      <c r="M95" s="5"/>
+      <c r="N95" s="5"/>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -4015,8 +5604,23 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H96" t="s">
+        <v>80</v>
+      </c>
+      <c r="I96" t="s">
+        <v>112</v>
+      </c>
+      <c r="J96" s="5">
+        <v>3</v>
+      </c>
+      <c r="K96" s="5">
+        <v>2</v>
+      </c>
+      <c r="L96" s="5"/>
+      <c r="M96" s="5"/>
+      <c r="N96" s="5"/>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -4040,8 +5644,29 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H97" t="s">
+        <v>92</v>
+      </c>
+      <c r="I97" t="s">
+        <v>114</v>
+      </c>
+      <c r="J97" s="5">
+        <v>0</v>
+      </c>
+      <c r="K97" s="5">
+        <v>0</v>
+      </c>
+      <c r="L97" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M97" s="5">
+        <v>4</v>
+      </c>
+      <c r="N97" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -4065,8 +5690,23 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H98" t="s">
+        <v>85</v>
+      </c>
+      <c r="I98" t="s">
+        <v>82</v>
+      </c>
+      <c r="J98" s="5">
+        <v>2</v>
+      </c>
+      <c r="K98" s="5">
+        <v>0</v>
+      </c>
+      <c r="L98" s="5"/>
+      <c r="M98" s="5"/>
+      <c r="N98" s="5"/>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -4090,8 +5730,23 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H99" t="s">
+        <v>88</v>
+      </c>
+      <c r="I99" t="s">
+        <v>81</v>
+      </c>
+      <c r="J99" s="5">
+        <v>2</v>
+      </c>
+      <c r="K99" s="5">
+        <v>1</v>
+      </c>
+      <c r="L99" s="5"/>
+      <c r="M99" s="5"/>
+      <c r="N99" s="5"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -4115,8 +5770,25 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H100" t="s">
+        <v>111</v>
+      </c>
+      <c r="I100" t="s">
+        <v>78</v>
+      </c>
+      <c r="J100" s="5">
+        <v>1</v>
+      </c>
+      <c r="K100" s="5">
+        <v>2</v>
+      </c>
+      <c r="L100" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M100" s="5"/>
+      <c r="N100" s="5"/>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -4140,8 +5812,25 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H101" t="s">
+        <v>80</v>
+      </c>
+      <c r="I101" t="s">
+        <v>92</v>
+      </c>
+      <c r="J101" s="5">
+        <v>3</v>
+      </c>
+      <c r="K101" s="5">
+        <v>1</v>
+      </c>
+      <c r="L101" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M101" s="5"/>
+      <c r="N101" s="5"/>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>101</v>
       </c>
@@ -4165,8 +5854,23 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H102" t="s">
+        <v>85</v>
+      </c>
+      <c r="I102" t="s">
+        <v>88</v>
+      </c>
+      <c r="J102" s="5">
+        <v>0</v>
+      </c>
+      <c r="K102" s="5">
+        <v>2</v>
+      </c>
+      <c r="L102" s="5"/>
+      <c r="M102" s="5"/>
+      <c r="N102" s="5"/>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>102</v>
       </c>
@@ -4190,8 +5894,23 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H103" t="s">
+        <v>78</v>
+      </c>
+      <c r="I103" t="s">
+        <v>80</v>
+      </c>
+      <c r="J103" s="5">
+        <v>1</v>
+      </c>
+      <c r="K103" s="5">
+        <v>2</v>
+      </c>
+      <c r="L103" s="5"/>
+      <c r="M103" s="5"/>
+      <c r="N103" s="5"/>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>103</v>
       </c>
@@ -4215,8 +5934,23 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H104" t="s">
+        <v>85</v>
+      </c>
+      <c r="I104" t="s">
+        <v>78</v>
+      </c>
+      <c r="J104" s="5">
+        <v>4</v>
+      </c>
+      <c r="K104" s="5">
+        <v>6</v>
+      </c>
+      <c r="L104" s="5"/>
+      <c r="M104" s="5"/>
+      <c r="N104" s="5"/>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>104</v>
       </c>
@@ -4240,6 +5974,23 @@
         <f>_xlfn.IFNA(INDEX(seeds[team],MATCH(matches[[#This Row],[away-seed]],seeds[seed],0)),"")</f>
         <v/>
       </c>
+      <c r="H105" t="s">
+        <v>88</v>
+      </c>
+      <c r="I105" t="s">
+        <v>80</v>
+      </c>
+      <c r="J105" s="5">
+        <v>1</v>
+      </c>
+      <c r="K105" s="5">
+        <v>0</v>
+      </c>
+      <c r="L105" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M105" s="5"/>
+      <c r="N105" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
